--- a/SGC-CKN/Excel/b435d68f-d84d-4f50-981d-a6be7853f540_Lô_đất_ký_hiệu_CT-02_P1-142_D800_21-03-2026.xlsx
+++ b/SGC-CKN/Excel/b435d68f-d84d-4f50-981d-a6be7853f540_Lô_đất_ký_hiệu_CT-02_P1-142_D800_21-03-2026.xlsx
@@ -125,7 +125,7 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">01:50
+    <t xml:space="preserve">01:30
 21/03/2026</t>
   </si>
   <si>
@@ -217,7 +217,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -248,12 +248,18 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FFC2410C"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <color rgb="FF78350F"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FFC2410C"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -300,7 +306,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -329,7 +335,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -345,6 +351,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA7F3D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -465,7 +476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -500,26 +511,20 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -557,13 +562,22 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1152,16 +1166,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-1.07</v>
+        <v>-0.07</v>
       </c>
       <c r="H11" s="5">
         <v>0.25</v>
       </c>
       <c r="I11" s="5">
-        <v>1.07</v>
+        <v>0.07</v>
       </c>
       <c r="J11" s="8">
-        <v>4.28</v>
+        <v>0.28</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1184,7 +1198,7 @@
         <v>33</v>
       </c>
       <c r="F12" s="9">
-        <v>-1.07</v>
+        <v>-0.07</v>
       </c>
       <c r="G12" s="9">
         <v>-4.17</v>
@@ -1193,10 +1207,10 @@
         <v>0.58</v>
       </c>
       <c r="I12" s="9">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="J12" s="12">
-        <v>5.31</v>
+        <v>7.03</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1225,207 +1239,207 @@
         <v>-7.47</v>
       </c>
       <c r="H13" s="13">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="I13" s="13">
         <v>3.3</v>
       </c>
-      <c r="J13" s="8">
-        <v>3.3</v>
+      <c r="J13" s="16">
+        <v>4.95</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="17">
         <v>-7.47</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="17">
         <v>-16.27</v>
       </c>
-      <c r="H14" s="16">
-        <v>1.17</v>
-      </c>
-      <c r="I14" s="16">
+      <c r="H14" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="I14" s="17">
         <v>8.8</v>
       </c>
       <c r="J14" s="12">
-        <v>7.54</v>
-      </c>
-      <c r="K14" s="17" t="s">
+        <v>5.87</v>
+      </c>
+      <c r="K14" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="20">
         <v>-16.27</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="20">
         <v>-21.47</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="20">
         <v>1</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="20">
         <v>5.2</v>
       </c>
       <c r="J15" s="12">
         <v>5.2</v>
       </c>
-      <c r="K15" s="20" t="s">
+      <c r="K15" s="21" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="23">
         <v>-21.47</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="23">
         <v>-25.47</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="23">
         <v>0.75</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="23">
         <v>4</v>
       </c>
       <c r="J16" s="12">
         <v>5.33</v>
       </c>
-      <c r="K16" s="23" t="s">
+      <c r="K16" s="24" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <v>-25.47</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="26">
         <v>-39.47</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="26">
         <v>3.83</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="26">
         <v>14</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="16">
         <v>3.65</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="K17" s="27" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="29">
         <v>-39.47</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="29">
         <v>-44.22</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="29">
         <v>0.67</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="29">
         <v>4.75</v>
       </c>
       <c r="J18" s="12">
         <v>7.13</v>
       </c>
-      <c r="K18" s="29" t="s">
+      <c r="K18" s="30" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1564,16 +1578,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-1.07</v>
+        <v>-0.07</v>
       </c>
       <c r="G2" s="5">
         <v>0.25</v>
       </c>
       <c r="H2" s="5">
-        <v>1.07</v>
+        <v>0.07</v>
       </c>
       <c r="I2" s="8">
-        <v>4.28</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1590,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-1.07</v>
+        <v>-0.07</v>
       </c>
       <c r="F3" s="9">
         <v>-4.17</v>
@@ -1599,10 +1613,10 @@
         <v>0.58</v>
       </c>
       <c r="H3" s="9">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="I3" s="12">
-        <v>5.31</v>
+        <v>7.03</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1625,67 +1639,67 @@
         <v>-7.47</v>
       </c>
       <c r="G4" s="13">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="H4" s="13">
         <v>3.3</v>
       </c>
-      <c r="I4" s="8">
-        <v>3.3</v>
+      <c r="I4" s="16">
+        <v>4.95</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="17">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="17">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="17">
         <v>-7.47</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="17">
         <v>-16.27</v>
       </c>
-      <c r="G5" s="16">
-        <v>1.17</v>
-      </c>
-      <c r="H5" s="16">
+      <c r="G5" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="H5" s="17">
         <v>8.8</v>
       </c>
       <c r="I5" s="12">
-        <v>7.54</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="20">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <v>-16.27</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="20">
         <v>-21.47</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="20">
         <v>1</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="20">
         <v>5.2</v>
       </c>
       <c r="I6" s="12">
@@ -1693,28 +1707,28 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="23">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="23">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="23">
         <v>-21.47</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="23">
         <v>-25.47</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="23">
         <v>0.75</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="23">
         <v>4</v>
       </c>
       <c r="I7" s="12">
@@ -1722,57 +1736,57 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="26">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <v>1</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <v>-25.47</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <v>-39.47</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="26">
         <v>3.83</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="26">
         <v>14</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="16">
         <v>3.65</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
+      <c r="A9" s="29">
         <v>8</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <v>1</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <v>-39.47</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="29">
         <v>-44.22</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="29">
         <v>0.67</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="29">
         <v>4.75</v>
       </c>
       <c r="I9" s="12">
@@ -1780,31 +1794,31 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <v>8</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="34">
         <v>0</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="34">
         <v>-44.22</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="34">
         <v>9.25</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10" s="34">
         <v>44.22</v>
       </c>
-      <c r="I10" s="33">
+      <c r="I10" s="34">
         <v>4.78</v>
       </c>
     </row>
